--- a/artfynd/A 32091-2020 artfynd.xlsx
+++ b/artfynd/A 32091-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32091-2020 artfynd.xlsx
+++ b/artfynd/A 32091-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,6 +1021,1036 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120477404</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515245</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7127940</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120476954</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515219</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7128001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120477902</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7127886</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120477976</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>515214</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7127928</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120477801</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>515240</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7127876</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120476999</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>515234</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7127990</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120478001</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>515193</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7127902</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120476917</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>515201</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7128011</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120476930</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>515211</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7128012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120478009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Över-Gissmansvattnet, Över-Gissmansvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>515189</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7127904</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32091-2020 artfynd.xlsx
+++ b/artfynd/A 32091-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120477404</v>
+        <v>120476954</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515245</v>
+        <v>515219</v>
       </c>
       <c r="R5" t="n">
-        <v>7127940</v>
+        <v>7128001</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,11 +1099,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120476954</v>
+        <v>120477404</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515219</v>
+        <v>515245</v>
       </c>
       <c r="R6" t="n">
-        <v>7128001</v>
+        <v>7127940</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,6 +1201,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120477902</v>
+        <v>120476930</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515250</v>
+        <v>515211</v>
       </c>
       <c r="R7" t="n">
-        <v>7127886</v>
+        <v>7128012</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,11 +1308,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120477976</v>
+        <v>120478009</v>
       </c>
       <c r="B8" t="n">
-        <v>90972</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,16 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515214</v>
+        <v>515189</v>
       </c>
       <c r="R8" t="n">
-        <v>7127928</v>
+        <v>7127904</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120477801</v>
+        <v>120477976</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90972</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1476,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515240</v>
+        <v>515214</v>
       </c>
       <c r="R9" t="n">
-        <v>7127876</v>
+        <v>7127928</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1512,11 +1507,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120476999</v>
+        <v>120476917</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,13 +1573,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515234</v>
+        <v>515201</v>
       </c>
       <c r="R10" t="n">
-        <v>7127990</v>
+        <v>7128011</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120478001</v>
+        <v>120477902</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,13 +1675,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515193</v>
+        <v>515250</v>
       </c>
       <c r="R11" t="n">
-        <v>7127902</v>
+        <v>7127886</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1721,6 +1711,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120476917</v>
+        <v>120477801</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,21 +1758,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515201</v>
+        <v>515240</v>
       </c>
       <c r="R12" t="n">
-        <v>7128011</v>
+        <v>7127876</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1823,6 +1818,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120476930</v>
+        <v>120478001</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515211</v>
+        <v>515193</v>
       </c>
       <c r="R13" t="n">
-        <v>7128012</v>
+        <v>7127902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120478009</v>
+        <v>120476999</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515189</v>
+        <v>515234</v>
       </c>
       <c r="R14" t="n">
-        <v>7127904</v>
+        <v>7127990</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 32091-2020 artfynd.xlsx
+++ b/artfynd/A 32091-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120476954</v>
+        <v>120477902</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515219</v>
+        <v>515250</v>
       </c>
       <c r="R5" t="n">
-        <v>7128001</v>
+        <v>7127886</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,6 +1099,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120477404</v>
+        <v>120477976</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1146,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515245</v>
+        <v>515214</v>
       </c>
       <c r="R6" t="n">
-        <v>7127940</v>
+        <v>7127928</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,11 +1201,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120476930</v>
+        <v>120478009</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1272,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515211</v>
+        <v>515189</v>
       </c>
       <c r="R7" t="n">
-        <v>7128012</v>
+        <v>7127904</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120478009</v>
+        <v>120476999</v>
       </c>
       <c r="B8" t="n">
         <v>79623</v>
@@ -1374,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515189</v>
+        <v>515234</v>
       </c>
       <c r="R8" t="n">
-        <v>7127904</v>
+        <v>7127990</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1436,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120477976</v>
+        <v>120476930</v>
       </c>
       <c r="B9" t="n">
-        <v>90972</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,16 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515214</v>
+        <v>515211</v>
       </c>
       <c r="R9" t="n">
-        <v>7127928</v>
+        <v>7128012</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120476917</v>
+        <v>120478001</v>
       </c>
       <c r="B10" t="n">
         <v>79624</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515201</v>
+        <v>515193</v>
       </c>
       <c r="R10" t="n">
-        <v>7128011</v>
+        <v>7127902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120477902</v>
+        <v>120477404</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515250</v>
+        <v>515245</v>
       </c>
       <c r="R11" t="n">
-        <v>7127886</v>
+        <v>7127940</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120477801</v>
+        <v>120476917</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515240</v>
+        <v>515201</v>
       </c>
       <c r="R12" t="n">
-        <v>7127876</v>
+        <v>7128011</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1818,11 +1818,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120478001</v>
+        <v>120476954</v>
       </c>
       <c r="B13" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,21 +1860,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515193</v>
+        <v>515219</v>
       </c>
       <c r="R13" t="n">
-        <v>7127902</v>
+        <v>7128001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120476999</v>
+        <v>120477801</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1962,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515234</v>
+        <v>515240</v>
       </c>
       <c r="R14" t="n">
-        <v>7127990</v>
+        <v>7127876</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2027,6 +2022,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 32091-2020 artfynd.xlsx
+++ b/artfynd/A 32091-2020 artfynd.xlsx
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120477902</v>
+        <v>120478001</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515250</v>
+        <v>515193</v>
       </c>
       <c r="R5" t="n">
-        <v>7127886</v>
+        <v>7127902</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,11 +1099,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120477976</v>
+        <v>120476930</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,16 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515214</v>
+        <v>515211</v>
       </c>
       <c r="R6" t="n">
-        <v>7127928</v>
+        <v>7128012</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120478009</v>
+        <v>120477902</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515189</v>
+        <v>515250</v>
       </c>
       <c r="R7" t="n">
-        <v>7127904</v>
+        <v>7127886</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1303,6 +1303,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120476999</v>
+        <v>120476917</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515234</v>
+        <v>515201</v>
       </c>
       <c r="R8" t="n">
-        <v>7127990</v>
+        <v>7128011</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120476930</v>
+        <v>120476999</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1471,13 +1476,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515211</v>
+        <v>515234</v>
       </c>
       <c r="R9" t="n">
-        <v>7128012</v>
+        <v>7127990</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120478001</v>
+        <v>120476954</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515193</v>
+        <v>515219</v>
       </c>
       <c r="R10" t="n">
-        <v>7127902</v>
+        <v>7128001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120477404</v>
+        <v>120477976</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,21 +1656,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515245</v>
+        <v>515214</v>
       </c>
       <c r="R11" t="n">
-        <v>7127940</v>
+        <v>7127928</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1711,11 +1711,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120476917</v>
+        <v>120478009</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,13 +1777,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515201</v>
+        <v>515189</v>
       </c>
       <c r="R12" t="n">
-        <v>7128011</v>
+        <v>7127904</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120476954</v>
+        <v>120477801</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1860,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,13 +1879,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515219</v>
+        <v>515240</v>
       </c>
       <c r="R13" t="n">
-        <v>7128001</v>
+        <v>7127876</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1920,6 +1915,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,7 +1946,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120477801</v>
+        <v>120477404</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515240</v>
+        <v>515245</v>
       </c>
       <c r="R14" t="n">
-        <v>7127876</v>
+        <v>7127940</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
